--- a/samples/ip_uc_import_template.xlsx
+++ b/samples/ip_uc_import_template.xlsx
@@ -1674,7 +1674,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>• คีย์ข้อมูลซ้ำ = งวด STM + ประเภทบริการ (ไม่สนตัวพิมพ์เล็ก/ใหญ่)</t>
+          <t>• ข้อมูลซ้ำ = งวด STM, เดือน, ปีงบประมาณ, ประเภทบริการ, ครั้ง(บริการ), Adj.RW ที่ชดเชย, ชดเชยก่อนหักเงินเดือน ตรงกันทั้ง 7 ฟิลด์ (ไม่เทียบค่า BR)</t>
         </is>
       </c>
     </row>
